--- a/Tools/DataTablesTool/DataTables/Datas/#UIPanel.xlsx
+++ b/Tools/DataTablesTool/DataTables/Datas/#UIPanel.xlsx
@@ -43,21 +43,12 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t xml:space="preserve">MJH:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>0:Overlay
+          <t>MJH:
+0:Overlay
 1：Camera</t>
         </r>
       </text>
@@ -66,20 +57,11 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="9"/>
+            <sz val="10"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>14047:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
+          <t>14047:
 0:YooAsset
 1:Resource</t>
         </r>
@@ -90,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -165,6 +147,60 @@
   </si>
   <si>
     <t>MainGroup</t>
+  </si>
+  <si>
+    <t>GameUI_PC</t>
+  </si>
+  <si>
+    <t>战斗HUD</t>
+  </si>
+  <si>
+    <t>BattleGroup</t>
+  </si>
+  <si>
+    <t>JoystickUI</t>
+  </si>
+  <si>
+    <t>摇杆</t>
+  </si>
+  <si>
+    <t>FadeScreen</t>
+  </si>
+  <si>
+    <t>淡入淡出</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>pause-ui</t>
+  </si>
+  <si>
+    <t>暂停</t>
+  </si>
+  <si>
+    <t>lose-ui</t>
+  </si>
+  <si>
+    <t>失败</t>
+  </si>
+  <si>
+    <t>win-ui</t>
+  </si>
+  <si>
+    <t>胜利</t>
+  </si>
+  <si>
+    <t>GemRewardUI</t>
+  </si>
+  <si>
+    <t>宝石奖励</t>
+  </si>
+  <si>
+    <t>message-1</t>
+  </si>
+  <si>
+    <t>提示消息</t>
   </si>
 </sst>
 </file>
@@ -177,7 +213,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -336,13 +372,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -797,24 +827,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1127,36 +1149,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="15.075" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="18.9583333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.775" style="1" customWidth="1"/>
-    <col min="7" max="8" width="21.55" customWidth="1"/>
-    <col min="9" max="9" width="14.1333333333333" customWidth="1"/>
-    <col min="10" max="10" width="24.2166666666667" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="15.075" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="18.9583333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.775" customWidth="1"/>
+    <col min="7" max="8" width="21.55" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.1333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.2166666666667" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
@@ -1170,96 +1192,95 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="5"/>
+      <c r="I4"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
@@ -1273,10 +1294,212 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1"/>
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>20</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="1"/>
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>25</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>80</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>60</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>70</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>70</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>75</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>50</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
